--- a/schoolDocs/StudentImportData/Class4_ImportReady.xlsx
+++ b/schoolDocs/StudentImportData/Class4_ImportReady.xlsx
@@ -817,27 +817,27 @@
   <dimension ref="A1:U30"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="9.283" bestFit="true" customWidth="true" style="0"/>
-    <col min="2" max="2" width="25.851" bestFit="true" customWidth="true" style="0"/>
-    <col min="3" max="3" width="18.71" bestFit="true" customWidth="true" style="0"/>
-    <col min="4" max="4" width="10.426" bestFit="true" customWidth="true" style="0"/>
-    <col min="5" max="5" width="9.283" bestFit="true" customWidth="true" style="0"/>
-    <col min="6" max="6" width="11.569" bestFit="true" customWidth="true" style="0"/>
-    <col min="7" max="7" width="25.708" bestFit="true" customWidth="true" style="0"/>
-    <col min="8" max="8" width="17.567" bestFit="true" customWidth="true" style="0"/>
-    <col min="9" max="9" width="15.139" bestFit="true" customWidth="true" style="0"/>
-    <col min="10" max="10" width="24.565" bestFit="true" customWidth="true" style="0"/>
-    <col min="11" max="11" width="29.279" bestFit="true" customWidth="true" style="0"/>
-    <col min="12" max="12" width="35.277" bestFit="true" customWidth="true" style="0"/>
-    <col min="13" max="13" width="15.282" bestFit="true" customWidth="true" style="0"/>
-    <col min="14" max="14" width="26.993" bestFit="true" customWidth="true" style="0"/>
-    <col min="15" max="15" width="16.282" bestFit="true" customWidth="true" style="0"/>
-    <col min="16" max="16" width="25.851" bestFit="true" customWidth="true" style="0"/>
-    <col min="17" max="17" width="16.282" bestFit="true" customWidth="true" style="0"/>
-    <col min="18" max="18" width="28.136" bestFit="true" customWidth="true" style="0"/>
-    <col min="19" max="19" width="15.139" bestFit="true" customWidth="true" style="0"/>
-    <col min="20" max="20" width="22.28" bestFit="true" customWidth="true" style="0"/>
-    <col min="21" max="21" width="89.55" bestFit="true" customWidth="true" style="0"/>
+    <col min="1" max="1" width="9.283" customWidth="true" style="0"/>
+    <col min="2" max="2" width="25.851" customWidth="true" style="0"/>
+    <col min="3" max="3" width="18.71" customWidth="true" style="0"/>
+    <col min="4" max="4" width="10.426" customWidth="true" style="0"/>
+    <col min="5" max="5" width="9.283" customWidth="true" style="0"/>
+    <col min="6" max="6" width="11.569" customWidth="true" style="0"/>
+    <col min="7" max="7" width="25.708" customWidth="true" style="0"/>
+    <col min="8" max="8" width="17.567" customWidth="true" style="0"/>
+    <col min="9" max="9" width="15.139" customWidth="true" style="0"/>
+    <col min="10" max="10" width="24.565" customWidth="true" style="0"/>
+    <col min="11" max="11" width="29.279" customWidth="true" style="0"/>
+    <col min="12" max="12" width="35.277" customWidth="true" style="0"/>
+    <col min="13" max="13" width="15.282" customWidth="true" style="0"/>
+    <col min="14" max="14" width="26.993" customWidth="true" style="0"/>
+    <col min="15" max="15" width="16.282" customWidth="true" style="0"/>
+    <col min="16" max="16" width="25.851" customWidth="true" style="0"/>
+    <col min="17" max="17" width="16.282" customWidth="true" style="0"/>
+    <col min="18" max="18" width="28.136" customWidth="true" style="0"/>
+    <col min="19" max="19" width="15.139" customWidth="true" style="0"/>
+    <col min="20" max="20" width="22.28" customWidth="true" style="0"/>
+    <col min="21" max="21" width="89.55" customWidth="true" style="0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:21" customHeight="1" ht="30">
@@ -924,6 +924,8 @@
       <c r="H2" t="s">
         <v>25</v>
       </c>
+      <c r="I2"/>
+      <c r="J2"/>
       <c r="K2">
         <v>16200</v>
       </c>
@@ -965,8 +967,10 @@
       <c r="H3" t="s">
         <v>25</v>
       </c>
+      <c r="I3"/>
+      <c r="J3"/>
       <c r="K3" s="5">
-        <v>5000</v>
+        <v>16200</v>
       </c>
       <c r="L3" t="s">
         <v>32</v>
@@ -1009,6 +1013,8 @@
       <c r="H4" t="s">
         <v>25</v>
       </c>
+      <c r="I4"/>
+      <c r="J4"/>
       <c r="K4">
         <v>16200</v>
       </c>
@@ -1050,6 +1056,11 @@
       <c r="H5" t="s">
         <v>25</v>
       </c>
+      <c r="I5"/>
+      <c r="J5"/>
+      <c r="K5">
+        <v>16200</v>
+      </c>
       <c r="L5" t="s">
         <v>43</v>
       </c>
@@ -1085,6 +1096,11 @@
       <c r="H6" t="s">
         <v>25</v>
       </c>
+      <c r="I6"/>
+      <c r="J6"/>
+      <c r="K6">
+        <v>16200</v>
+      </c>
       <c r="L6" t="s">
         <v>46</v>
       </c>
@@ -1120,6 +1136,8 @@
       <c r="H7" t="s">
         <v>25</v>
       </c>
+      <c r="I7"/>
+      <c r="J7"/>
       <c r="K7">
         <v>16200</v>
       </c>
@@ -1161,6 +1179,11 @@
       <c r="H8" t="s">
         <v>25</v>
       </c>
+      <c r="I8"/>
+      <c r="J8"/>
+      <c r="K8">
+        <v>16200</v>
+      </c>
       <c r="L8" t="s">
         <v>32</v>
       </c>
@@ -1199,6 +1222,11 @@
       <c r="H9" t="s">
         <v>56</v>
       </c>
+      <c r="I9"/>
+      <c r="J9"/>
+      <c r="K9">
+        <v>0</v>
+      </c>
       <c r="L9" t="s">
         <v>57</v>
       </c>
@@ -1234,6 +1262,11 @@
       <c r="H10" t="s">
         <v>25</v>
       </c>
+      <c r="I10"/>
+      <c r="J10"/>
+      <c r="K10">
+        <v>16200</v>
+      </c>
       <c r="L10" t="s">
         <v>60</v>
       </c>
@@ -1272,8 +1305,9 @@
       <c r="I11">
         <v>25</v>
       </c>
+      <c r="J11"/>
       <c r="K11">
-        <v>12150</v>
+        <v>6000</v>
       </c>
       <c r="L11" t="s">
         <v>66</v>
@@ -1310,11 +1344,12 @@
       <c r="H12" t="s">
         <v>65</v>
       </c>
+      <c r="I12"/>
       <c r="J12">
         <v>8000</v>
       </c>
       <c r="K12">
-        <v>8000</v>
+        <v>8000.0</v>
       </c>
       <c r="L12" t="s">
         <v>32</v>
@@ -1354,6 +1389,11 @@
       <c r="H13" t="s">
         <v>71</v>
       </c>
+      <c r="I13"/>
+      <c r="J13"/>
+      <c r="K13">
+        <v>16200</v>
+      </c>
       <c r="L13" t="s">
         <v>72</v>
       </c>
@@ -1386,6 +1426,8 @@
       <c r="H14" t="s">
         <v>71</v>
       </c>
+      <c r="I14"/>
+      <c r="J14"/>
       <c r="K14">
         <v>16200</v>
       </c>
@@ -1415,8 +1457,10 @@
       <c r="H15" t="s">
         <v>71</v>
       </c>
+      <c r="I15"/>
+      <c r="J15"/>
       <c r="K15">
-        <v>12200</v>
+        <v>16200</v>
       </c>
       <c r="L15" t="s">
         <v>80</v>
@@ -1447,6 +1491,11 @@
       <c r="H16" t="s">
         <v>56</v>
       </c>
+      <c r="I16"/>
+      <c r="J16"/>
+      <c r="K16">
+        <v>0</v>
+      </c>
       <c r="L16" t="s">
         <v>83</v>
       </c>
@@ -1488,6 +1537,11 @@
       <c r="H17" t="s">
         <v>56</v>
       </c>
+      <c r="I17"/>
+      <c r="J17"/>
+      <c r="K17">
+        <v>0</v>
+      </c>
       <c r="L17" t="s">
         <v>88</v>
       </c>
@@ -1523,8 +1577,9 @@
       <c r="I18">
         <v>25</v>
       </c>
+      <c r="J18"/>
       <c r="K18">
-        <v>3150</v>
+        <v>9150</v>
       </c>
       <c r="L18" t="s">
         <v>90</v>
@@ -1564,6 +1619,8 @@
       <c r="H19" t="s">
         <v>25</v>
       </c>
+      <c r="I19"/>
+      <c r="J19"/>
       <c r="K19">
         <v>12200</v>
       </c>
@@ -1611,6 +1668,10 @@
       <c r="I20">
         <v>25</v>
       </c>
+      <c r="J20"/>
+      <c r="K20">
+        <v>9150</v>
+      </c>
       <c r="L20" t="s">
         <v>98</v>
       </c>
@@ -1652,6 +1713,7 @@
       <c r="I21">
         <v>25</v>
       </c>
+      <c r="J21"/>
       <c r="K21">
         <v>9150</v>
       </c>
@@ -1696,6 +1758,10 @@
       <c r="I22">
         <v>25</v>
       </c>
+      <c r="J22"/>
+      <c r="K22">
+        <v>9150</v>
+      </c>
       <c r="L22" t="s">
         <v>104</v>
       </c>
@@ -1737,6 +1803,7 @@
       <c r="I23">
         <v>25</v>
       </c>
+      <c r="J23"/>
       <c r="K23">
         <v>9150</v>
       </c>
@@ -1778,8 +1845,10 @@
       <c r="H24" t="s">
         <v>25</v>
       </c>
+      <c r="I24"/>
+      <c r="J24"/>
       <c r="K24">
-        <v>8200</v>
+        <v>12200</v>
       </c>
       <c r="L24" t="s">
         <v>109</v>
@@ -1822,8 +1891,9 @@
       <c r="I25">
         <v>25</v>
       </c>
+      <c r="J25"/>
       <c r="K25">
-        <v>4100</v>
+        <v>9150</v>
       </c>
       <c r="L25" t="s">
         <v>116</v>
@@ -1866,11 +1936,12 @@
       <c r="H26" t="s">
         <v>65</v>
       </c>
+      <c r="I26"/>
       <c r="J26">
         <v>11000</v>
       </c>
       <c r="K26" s="5">
-        <v>11000</v>
+        <v>11000.0</v>
       </c>
       <c r="L26" t="s">
         <v>120</v>
@@ -1913,11 +1984,12 @@
       <c r="H27" t="s">
         <v>65</v>
       </c>
+      <c r="I27"/>
       <c r="J27">
         <v>10000</v>
       </c>
       <c r="K27">
-        <v>10000</v>
+        <v>10000.0</v>
       </c>
       <c r="L27" t="s">
         <v>125</v>
@@ -1951,6 +2023,11 @@
       <c r="H28" t="s">
         <v>25</v>
       </c>
+      <c r="I28"/>
+      <c r="J28"/>
+      <c r="K28">
+        <v>12200</v>
+      </c>
       <c r="L28" t="s">
         <v>107</v>
       </c>
@@ -1990,8 +2067,9 @@
       <c r="I29">
         <v>25</v>
       </c>
+      <c r="J29"/>
       <c r="K29">
-        <v>6100</v>
+        <v>9150</v>
       </c>
       <c r="L29" t="s">
         <v>131</v>
@@ -2027,6 +2105,11 @@
       </c>
       <c r="H30" t="s">
         <v>56</v>
+      </c>
+      <c r="I30"/>
+      <c r="J30"/>
+      <c r="K30">
+        <v>0</v>
       </c>
       <c r="L30" t="s">
         <v>134</v>

--- a/schoolDocs/StudentImportData/Class4_ImportReady.xlsx
+++ b/schoolDocs/StudentImportData/Class4_ImportReady.xlsx
@@ -14,8 +14,34 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Author</author>
+  </authors>
+  <commentList>
+    <comment ref="U1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <rFont val="Calibri"/>
+            <b val="false"/>
+            <i val="false"/>
+            <strike val="false"/>
+            <color rgb="FF000000"/>
+            <sz val="11"/>
+            <u val="none"/>
+          </rPr>
+          <t xml:space="preserve">Only for RTE students. Alphanumeric, e.g. 26MS011157 (Year+StateCode+Sequence). Leave blank for non-RTE.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="122">
   <si>
     <t>Sr No</t>
   </si>
@@ -77,7 +103,7 @@
     <t>DGA Admission No</t>
   </si>
   <si>
-    <t>Notes for Verification (ignored on import)</t>
+    <t>RTE Application No</t>
   </si>
   <si>
     <t>Swaraj Gadade</t>
@@ -125,9 +151,6 @@
     <t>Beauty Parlour</t>
   </si>
   <si>
-    <t>Partial — ₹5000 of ₹16200 collected</t>
-  </si>
-  <si>
     <t>Rajvir Dhaygude</t>
   </si>
   <si>
@@ -191,7 +214,7 @@
     <t>20/01/2022</t>
   </si>
   <si>
-    <t>RTE — fees paid by government</t>
+    <t>25MS000026</t>
   </si>
   <si>
     <t>Sairaj Memane</t>
@@ -218,15 +241,9 @@
     <t>22/12/2021</t>
   </si>
   <si>
-    <t>Discount 25% on boys fee ₹16200 = ₹12150 payable — full paid</t>
-  </si>
-  <si>
     <t>Aryan Chaurasiya</t>
   </si>
   <si>
-    <t>DGA G=0.5 (50%) but total ₹8000 — using ₹8000 as custom fee. Please verify.</t>
-  </si>
-  <si>
     <t>Viraj Kshirsagar</t>
   </si>
   <si>
@@ -242,27 +259,18 @@
     <t>19km</t>
   </si>
   <si>
-    <t>CoC student — ₹0 collected</t>
-  </si>
-  <si>
     <t>Adil Shaikh</t>
   </si>
   <si>
     <t>01/12/2019</t>
   </si>
   <si>
-    <t>CoC student — full ₹16200 collected</t>
-  </si>
-  <si>
     <t>Sahil Kashid</t>
   </si>
   <si>
     <t>25/12/2021</t>
   </si>
   <si>
-    <t>DGA shows ₹12200 for this CoC boy — system will use ₹16200. Please verify.</t>
-  </si>
-  <si>
     <t>Prathmesh Bhosale</t>
   </si>
   <si>
@@ -272,7 +280,7 @@
     <t>Road seller</t>
   </si>
   <si>
-    <t>Class column blank in DGA sheet — assumed Class 4. Please verify.</t>
+    <t>25MS000027</t>
   </si>
   <si>
     <t>Manasvi Sonavane</t>
@@ -284,6 +292,9 @@
     <t>24/12/2019</t>
   </si>
   <si>
+    <t>25MS000028</t>
+  </si>
+  <si>
     <t>Aliya Ansari</t>
   </si>
   <si>
@@ -293,9 +304,6 @@
     <t>Works at Bakery Shop</t>
   </si>
   <si>
-    <t>Discount 25% on girls ₹12200 = ₹9150 payable — collected ₹3150 (partial)</t>
-  </si>
-  <si>
     <t>Anushka Shinge</t>
   </si>
   <si>
@@ -305,9 +313,6 @@
     <t>Chef</t>
   </si>
   <si>
-    <t>Contact in DGA was 9 digits (invalid) — left blank</t>
-  </si>
-  <si>
     <t>Swara Ghogare</t>
   </si>
   <si>
@@ -317,15 +322,9 @@
     <t>Labour</t>
   </si>
   <si>
-    <t>Discount 25% on girls ₹12200 = ₹9150 payable — collected ₹0</t>
-  </si>
-  <si>
     <t>Lochana Chaudhari</t>
   </si>
   <si>
-    <t>Discount 25% on girls ₹12200 = ₹9150 payable — full paid</t>
-  </si>
-  <si>
     <t>Sanam Tamboli</t>
   </si>
   <si>
@@ -359,9 +358,6 @@
     <t>Works at own farm</t>
   </si>
   <si>
-    <t>Partial — ₹8200 of ₹12200 collected</t>
-  </si>
-  <si>
     <t>Pranjal Baravkar</t>
   </si>
   <si>
@@ -371,9 +367,6 @@
     <t>General store</t>
   </si>
   <si>
-    <t>Discount 25% on girls ₹12200 = ₹9150 payable — collected ₹4100 (partial)</t>
-  </si>
-  <si>
     <t>Aarohi Aade</t>
   </si>
   <si>
@@ -386,9 +379,6 @@
     <t>Worker</t>
   </si>
   <si>
-    <t>DGA shows discount but no % — ₹11000 used as custom fee. Please verify.</t>
-  </si>
-  <si>
     <t>Archana Gaikwad</t>
   </si>
   <si>
@@ -401,9 +391,6 @@
     <t>11km</t>
   </si>
   <si>
-    <t>DGA shows discount but no % — ₹10000 used as custom fee. Please verify.</t>
-  </si>
-  <si>
     <t>Riya Awasare</t>
   </si>
   <si>
@@ -413,13 +400,13 @@
     <t>13/12/2021</t>
   </si>
   <si>
-    <t>Discount 25% on girls ₹12200 = ₹9150 payable — collected ₹6100 (partial)</t>
-  </si>
-  <si>
     <t>Aarju Sayyad</t>
   </si>
   <si>
     <t>04/02/2020</t>
+  </si>
+  <si>
+    <t>25MS000029</t>
   </si>
 </sst>
 </file>
@@ -471,12 +458,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF7B3F00"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFF3CD"/>
         <bgColor rgb="FF000000"/>
       </patternFill>
@@ -484,6 +465,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD5EAD0"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2E4057"/>
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
@@ -505,16 +492,16 @@
     <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="3" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="3" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="2" numFmtId="0" fillId="4" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="5" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="3" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="5" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="4" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -837,7 +824,7 @@
     <col min="18" max="18" width="28.136" customWidth="true" style="0"/>
     <col min="19" max="19" width="15.139" customWidth="true" style="0"/>
     <col min="20" max="20" width="22.28" customWidth="true" style="0"/>
-    <col min="21" max="21" width="89.55" customWidth="true" style="0"/>
+    <col min="21" max="21" width="20" customWidth="true" style="0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:21" customHeight="1" ht="30">
@@ -871,10 +858,10 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="L1" s="3" t="s">
         <v>11</v>
       </c>
       <c r="M1" s="1" t="s">
@@ -901,7 +888,7 @@
       <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="2" t="s">
+      <c r="U1" s="5" t="s">
         <v>20</v>
       </c>
     </row>
@@ -944,6 +931,7 @@
       <c r="R2" t="s">
         <v>30</v>
       </c>
+      <c r="U2"/>
     </row>
     <row r="3" spans="1:21">
       <c r="A3">
@@ -969,7 +957,7 @@
       </c>
       <c r="I3"/>
       <c r="J3"/>
-      <c r="K3" s="5">
+      <c r="K3" s="4">
         <v>16200</v>
       </c>
       <c r="L3" t="s">
@@ -987,16 +975,14 @@
       <c r="R3" t="s">
         <v>35</v>
       </c>
-      <c r="U3" t="s">
-        <v>36</v>
-      </c>
+      <c r="U3"/>
     </row>
     <row r="4" spans="1:21">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D4" t="s">
         <v>22</v>
@@ -1019,27 +1005,28 @@
         <v>16200</v>
       </c>
       <c r="L4" t="s">
+        <v>37</v>
+      </c>
+      <c r="M4" t="s">
         <v>38</v>
       </c>
-      <c r="M4" t="s">
+      <c r="N4" t="s">
         <v>39</v>
       </c>
-      <c r="N4" t="s">
+      <c r="P4" t="s">
         <v>40</v>
-      </c>
-      <c r="P4" t="s">
-        <v>41</v>
       </c>
       <c r="R4" t="s">
         <v>30</v>
       </c>
+      <c r="U4"/>
     </row>
     <row r="5" spans="1:21">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D5" t="s">
         <v>22</v>
@@ -1062,7 +1049,7 @@
         <v>16200</v>
       </c>
       <c r="L5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M5" t="s">
         <v>33</v>
@@ -1071,18 +1058,19 @@
         <v>28</v>
       </c>
       <c r="P5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="R5" t="s">
         <v>30</v>
       </c>
+      <c r="U5"/>
     </row>
     <row r="6" spans="1:21">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D6" t="s">
         <v>22</v>
@@ -1102,27 +1090,28 @@
         <v>16200</v>
       </c>
       <c r="L6" t="s">
+        <v>45</v>
+      </c>
+      <c r="M6" t="s">
         <v>46</v>
       </c>
-      <c r="M6" t="s">
+      <c r="N6" t="s">
         <v>47</v>
       </c>
-      <c r="N6" t="s">
+      <c r="P6" t="s">
         <v>48</v>
-      </c>
-      <c r="P6" t="s">
-        <v>49</v>
       </c>
       <c r="R6" t="s">
         <v>34</v>
       </c>
+      <c r="U6"/>
     </row>
     <row r="7" spans="1:21">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D7" t="s">
         <v>22</v>
@@ -1142,7 +1131,7 @@
         <v>16200</v>
       </c>
       <c r="L7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="M7" t="s">
         <v>33</v>
@@ -1151,18 +1140,19 @@
         <v>28</v>
       </c>
       <c r="P7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="R7" t="s">
         <v>30</v>
       </c>
+      <c r="U7"/>
     </row>
     <row r="8" spans="1:21">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D8" t="s">
         <v>22</v>
@@ -1188,24 +1178,25 @@
         <v>32</v>
       </c>
       <c r="M8" t="s">
+        <v>38</v>
+      </c>
+      <c r="N8" t="s">
         <v>39</v>
       </c>
-      <c r="N8" t="s">
-        <v>40</v>
-      </c>
       <c r="P8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="R8" t="s">
         <v>30</v>
       </c>
+      <c r="U8"/>
     </row>
     <row r="9" spans="1:21">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D9" t="s">
         <v>22</v>
@@ -1220,7 +1211,7 @@
         <v>9730004940</v>
       </c>
       <c r="H9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I9"/>
       <c r="J9"/>
@@ -1228,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M9" t="s">
         <v>33</v>
@@ -1237,7 +1228,7 @@
         <v>28</v>
       </c>
       <c r="U9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="10" spans="1:21">
@@ -1245,7 +1236,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D10" t="s">
         <v>22</v>
@@ -1268,24 +1259,25 @@
         <v>16200</v>
       </c>
       <c r="L10" t="s">
+        <v>59</v>
+      </c>
+      <c r="M10" t="s">
         <v>60</v>
       </c>
-      <c r="M10" t="s">
+      <c r="N10" t="s">
         <v>61</v>
       </c>
-      <c r="N10" t="s">
+      <c r="R10" t="s">
         <v>62</v>
       </c>
-      <c r="R10" t="s">
-        <v>63</v>
-      </c>
+      <c r="U10"/>
     </row>
     <row r="11" spans="1:21">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D11" t="s">
         <v>22</v>
@@ -1300,7 +1292,7 @@
         <v>8485054355</v>
       </c>
       <c r="H11" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I11">
         <v>25</v>
@@ -1310,24 +1302,22 @@
         <v>6000</v>
       </c>
       <c r="L11" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="M11" t="s">
+        <v>38</v>
+      </c>
+      <c r="N11" t="s">
         <v>39</v>
       </c>
-      <c r="N11" t="s">
-        <v>40</v>
-      </c>
-      <c r="U11" t="s">
-        <v>67</v>
-      </c>
+      <c r="U11"/>
     </row>
     <row r="12" spans="1:21">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D12" t="s">
         <v>22</v>
@@ -1342,7 +1332,7 @@
         <v>8545074211</v>
       </c>
       <c r="H12" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I12"/>
       <c r="J12">
@@ -1355,27 +1345,25 @@
         <v>32</v>
       </c>
       <c r="M12" t="s">
+        <v>46</v>
+      </c>
+      <c r="N12" t="s">
         <v>47</v>
       </c>
-      <c r="N12" t="s">
+      <c r="P12" t="s">
         <v>48</v>
-      </c>
-      <c r="P12" t="s">
-        <v>49</v>
       </c>
       <c r="R12" t="s">
         <v>30</v>
       </c>
-      <c r="U12" t="s">
-        <v>69</v>
-      </c>
+      <c r="U12"/>
     </row>
     <row r="13" spans="1:21">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D13" t="s">
         <v>22</v>
@@ -1387,7 +1375,7 @@
         <v>24</v>
       </c>
       <c r="H13" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="I13"/>
       <c r="J13"/>
@@ -1395,24 +1383,22 @@
         <v>16200</v>
       </c>
       <c r="L13" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="M13" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="N13" t="s">
-        <v>74</v>
-      </c>
-      <c r="U13" s="5" t="s">
-        <v>75</v>
-      </c>
+        <v>71</v>
+      </c>
+      <c r="U13" s="4"/>
     </row>
     <row r="14" spans="1:21">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D14" t="s">
         <v>22</v>
@@ -1424,7 +1410,7 @@
         <v>24</v>
       </c>
       <c r="H14" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="I14"/>
       <c r="J14"/>
@@ -1432,18 +1418,16 @@
         <v>16200</v>
       </c>
       <c r="L14" t="s">
-        <v>77</v>
-      </c>
-      <c r="U14" t="s">
-        <v>78</v>
-      </c>
+        <v>73</v>
+      </c>
+      <c r="U14"/>
     </row>
     <row r="15" spans="1:21">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="D15" t="s">
         <v>22</v>
@@ -1455,7 +1439,7 @@
         <v>24</v>
       </c>
       <c r="H15" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="I15"/>
       <c r="J15"/>
@@ -1463,18 +1447,16 @@
         <v>16200</v>
       </c>
       <c r="L15" t="s">
-        <v>80</v>
-      </c>
-      <c r="U15" t="s">
-        <v>81</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="U15"/>
     </row>
     <row r="16" spans="1:21">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="D16" t="s">
         <v>22</v>
@@ -1489,7 +1471,7 @@
         <v>9766444535</v>
       </c>
       <c r="H16" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I16"/>
       <c r="J16"/>
@@ -1497,7 +1479,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="M16" t="s">
         <v>33</v>
@@ -1506,13 +1488,13 @@
         <v>28</v>
       </c>
       <c r="P16" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="R16" t="s">
         <v>30</v>
       </c>
-      <c r="U16" s="5" t="s">
-        <v>85</v>
+      <c r="U16" s="4" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="17" spans="1:21">
@@ -1520,10 +1502,10 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="D17" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="E17" t="s">
         <v>23</v>
@@ -1535,7 +1517,7 @@
         <v>9960184120</v>
       </c>
       <c r="H17" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I17"/>
       <c r="J17"/>
@@ -1543,7 +1525,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="M17" t="s">
         <v>27</v>
@@ -1552,7 +1534,7 @@
         <v>28</v>
       </c>
       <c r="U17" t="s">
-        <v>58</v>
+        <v>83</v>
       </c>
     </row>
     <row r="18" spans="1:21">
@@ -1560,10 +1542,10 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="D18" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="E18" t="s">
         <v>23</v>
@@ -1572,7 +1554,7 @@
         <v>24</v>
       </c>
       <c r="H18" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I18">
         <v>25</v>
@@ -1582,33 +1564,31 @@
         <v>9150</v>
       </c>
       <c r="L18" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="M18" t="s">
+        <v>38</v>
+      </c>
+      <c r="N18" t="s">
         <v>39</v>
       </c>
-      <c r="N18" t="s">
-        <v>40</v>
-      </c>
       <c r="P18" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="R18" t="s">
         <v>30</v>
       </c>
-      <c r="U18" t="s">
-        <v>92</v>
-      </c>
+      <c r="U18"/>
     </row>
     <row r="19" spans="1:21">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="D19" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="E19" t="s">
         <v>23</v>
@@ -1625,7 +1605,7 @@
         <v>12200</v>
       </c>
       <c r="L19" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="M19" t="s">
         <v>33</v>
@@ -1634,24 +1614,22 @@
         <v>28</v>
       </c>
       <c r="P19" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="R19" t="s">
         <v>30</v>
       </c>
-      <c r="U19" t="s">
-        <v>96</v>
-      </c>
+      <c r="U19"/>
     </row>
     <row r="20" spans="1:21">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="D20" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="E20" t="s">
         <v>23</v>
@@ -1663,7 +1641,7 @@
         <v>9823827707</v>
       </c>
       <c r="H20" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I20">
         <v>25</v>
@@ -1673,33 +1651,31 @@
         <v>9150</v>
       </c>
       <c r="L20" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="M20" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="N20" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="P20" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="R20" t="s">
         <v>30</v>
       </c>
-      <c r="U20" t="s">
-        <v>100</v>
-      </c>
+      <c r="U20"/>
     </row>
     <row r="21" spans="1:21">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="D21" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="E21" t="s">
         <v>23</v>
@@ -1708,7 +1684,7 @@
         <v>24</v>
       </c>
       <c r="H21" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I21">
         <v>25</v>
@@ -1718,33 +1694,31 @@
         <v>9150</v>
       </c>
       <c r="L21" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="M21" t="s">
+        <v>46</v>
+      </c>
+      <c r="N21" t="s">
         <v>47</v>
       </c>
-      <c r="N21" t="s">
+      <c r="P21" t="s">
         <v>48</v>
-      </c>
-      <c r="P21" t="s">
-        <v>49</v>
       </c>
       <c r="R21" t="s">
         <v>30</v>
       </c>
-      <c r="U21" t="s">
-        <v>102</v>
-      </c>
+      <c r="U21"/>
     </row>
     <row r="22" spans="1:21">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="D22" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="E22" t="s">
         <v>23</v>
@@ -1753,7 +1727,7 @@
         <v>24</v>
       </c>
       <c r="H22" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I22">
         <v>25</v>
@@ -1763,33 +1737,31 @@
         <v>9150</v>
       </c>
       <c r="L22" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="M22" t="s">
+        <v>38</v>
+      </c>
+      <c r="N22" t="s">
         <v>39</v>
       </c>
-      <c r="N22" t="s">
-        <v>40</v>
-      </c>
       <c r="P22" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="R22" t="s">
         <v>30</v>
       </c>
-      <c r="U22" t="s">
-        <v>100</v>
-      </c>
+      <c r="U22"/>
     </row>
     <row r="23" spans="1:21">
       <c r="A23">
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="D23" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="E23" t="s">
         <v>23</v>
@@ -1798,7 +1770,7 @@
         <v>24</v>
       </c>
       <c r="H23" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I23">
         <v>25</v>
@@ -1808,33 +1780,31 @@
         <v>9150</v>
       </c>
       <c r="L23" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="M23" t="s">
+        <v>38</v>
+      </c>
+      <c r="N23" t="s">
         <v>39</v>
       </c>
-      <c r="N23" t="s">
-        <v>40</v>
-      </c>
       <c r="P23" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="R23" t="s">
         <v>30</v>
       </c>
-      <c r="U23" t="s">
-        <v>102</v>
-      </c>
+      <c r="U23"/>
     </row>
     <row r="24" spans="1:21">
       <c r="A24">
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="D24" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="E24" t="s">
         <v>23</v>
@@ -1851,33 +1821,31 @@
         <v>12200</v>
       </c>
       <c r="L24" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="M24" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="N24" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="P24" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="R24" t="s">
-        <v>113</v>
-      </c>
-      <c r="U24" t="s">
-        <v>114</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="U24"/>
     </row>
     <row r="25" spans="1:21">
       <c r="A25">
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="D25" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="E25" t="s">
         <v>23</v>
@@ -1886,7 +1854,7 @@
         <v>24</v>
       </c>
       <c r="H25" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I25">
         <v>25</v>
@@ -1896,33 +1864,31 @@
         <v>9150</v>
       </c>
       <c r="L25" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="M25" t="s">
+        <v>38</v>
+      </c>
+      <c r="N25" t="s">
         <v>39</v>
       </c>
-      <c r="N25" t="s">
-        <v>40</v>
-      </c>
       <c r="P25" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="R25" t="s">
-        <v>117</v>
-      </c>
-      <c r="U25" t="s">
-        <v>118</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="U25"/>
     </row>
     <row r="26" spans="1:21">
       <c r="A26">
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="D26" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="E26" t="s">
         <v>23</v>
@@ -1934,43 +1900,41 @@
         <v>7709642604</v>
       </c>
       <c r="H26" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I26"/>
       <c r="J26">
         <v>11000</v>
       </c>
-      <c r="K26" s="5">
+      <c r="K26" s="4">
         <v>11000.0</v>
       </c>
       <c r="L26" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="M26" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="N26" t="s">
         <v>28</v>
       </c>
       <c r="P26" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="R26" t="s">
         <v>30</v>
       </c>
-      <c r="U26" t="s">
-        <v>123</v>
-      </c>
+      <c r="U26"/>
     </row>
     <row r="27" spans="1:21">
       <c r="A27">
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="D27" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="E27" t="s">
         <v>23</v>
@@ -1982,7 +1946,7 @@
         <v>8788402403</v>
       </c>
       <c r="H27" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I27"/>
       <c r="J27">
@@ -1992,27 +1956,25 @@
         <v>10000.0</v>
       </c>
       <c r="L27" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="M27" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="N27" t="s">
-        <v>127</v>
-      </c>
-      <c r="U27" s="5" t="s">
-        <v>128</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="U27" s="4"/>
     </row>
     <row r="28" spans="1:21">
       <c r="A28">
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>129</v>
+        <v>116</v>
       </c>
       <c r="D28" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="E28" t="s">
         <v>23</v>
@@ -2029,7 +1991,7 @@
         <v>12200</v>
       </c>
       <c r="L28" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="M28" t="s">
         <v>27</v>
@@ -2038,22 +2000,22 @@
         <v>28</v>
       </c>
       <c r="P28" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="R28" t="s">
-        <v>122</v>
-      </c>
-      <c r="U28" s="5"/>
+        <v>111</v>
+      </c>
+      <c r="U28" s="4"/>
     </row>
     <row r="29" spans="1:21">
       <c r="A29">
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>130</v>
+        <v>117</v>
       </c>
       <c r="D29" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="E29" t="s">
         <v>23</v>
@@ -2062,7 +2024,7 @@
         <v>24</v>
       </c>
       <c r="H29" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I29">
         <v>25</v>
@@ -2072,7 +2034,7 @@
         <v>9150</v>
       </c>
       <c r="L29" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="M29" t="s">
         <v>27</v>
@@ -2080,19 +2042,17 @@
       <c r="N29" t="s">
         <v>28</v>
       </c>
-      <c r="U29" t="s">
-        <v>132</v>
-      </c>
+      <c r="U29"/>
     </row>
     <row r="30" spans="1:21">
       <c r="A30">
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>133</v>
+        <v>119</v>
       </c>
       <c r="D30" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="E30" t="s">
         <v>23</v>
@@ -2104,7 +2064,7 @@
         <v>7822936079</v>
       </c>
       <c r="H30" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I30"/>
       <c r="J30"/>
@@ -2112,22 +2072,22 @@
         <v>0</v>
       </c>
       <c r="L30" t="s">
-        <v>134</v>
+        <v>120</v>
       </c>
       <c r="M30" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="N30" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="P30" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="R30" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="U30" t="s">
-        <v>58</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>
@@ -2142,6 +2102,7 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
+  <legacyDrawing r:id="rId_comments_vml1"/>
   <tableParts count="0"/>
 </worksheet>
 </file>
--- a/schoolDocs/StudentImportData/Class4_ImportReady.xlsx
+++ b/schoolDocs/StudentImportData/Class4_ImportReady.xlsx
@@ -931,6 +931,9 @@
       <c r="R2" t="s">
         <v>30</v>
       </c>
+      <c r="S2">
+        <v>27000010059</v>
+      </c>
       <c r="U2"/>
     </row>
     <row r="3" spans="1:21">
@@ -975,6 +978,9 @@
       <c r="R3" t="s">
         <v>35</v>
       </c>
+      <c r="S3">
+        <v>27000010060</v>
+      </c>
       <c r="U3"/>
     </row>
     <row r="4" spans="1:21">
@@ -1019,6 +1025,9 @@
       <c r="R4" t="s">
         <v>30</v>
       </c>
+      <c r="S4">
+        <v>27000010061</v>
+      </c>
       <c r="U4"/>
     </row>
     <row r="5" spans="1:21">
@@ -1063,6 +1072,9 @@
       <c r="R5" t="s">
         <v>30</v>
       </c>
+      <c r="S5">
+        <v>27000010062</v>
+      </c>
       <c r="U5"/>
     </row>
     <row r="6" spans="1:21">
@@ -1104,6 +1116,9 @@
       <c r="R6" t="s">
         <v>34</v>
       </c>
+      <c r="S6">
+        <v>27000010063</v>
+      </c>
       <c r="U6"/>
     </row>
     <row r="7" spans="1:21">
@@ -1145,6 +1160,9 @@
       <c r="R7" t="s">
         <v>30</v>
       </c>
+      <c r="S7">
+        <v>27000010064</v>
+      </c>
       <c r="U7"/>
     </row>
     <row r="8" spans="1:21">
@@ -1189,6 +1207,9 @@
       <c r="R8" t="s">
         <v>30</v>
       </c>
+      <c r="S8">
+        <v>27000010065</v>
+      </c>
       <c r="U8"/>
     </row>
     <row r="9" spans="1:21">
@@ -1227,6 +1248,9 @@
       <c r="N9" t="s">
         <v>28</v>
       </c>
+      <c r="S9">
+        <v>27000010066</v>
+      </c>
       <c r="U9" t="s">
         <v>57</v>
       </c>
@@ -1270,6 +1294,9 @@
       <c r="R10" t="s">
         <v>62</v>
       </c>
+      <c r="S10">
+        <v>27000010067</v>
+      </c>
       <c r="U10"/>
     </row>
     <row r="11" spans="1:21">
@@ -1310,6 +1337,9 @@
       <c r="N11" t="s">
         <v>39</v>
       </c>
+      <c r="S11">
+        <v>27000010068</v>
+      </c>
       <c r="U11"/>
     </row>
     <row r="12" spans="1:21">
@@ -1355,6 +1385,9 @@
       </c>
       <c r="R12" t="s">
         <v>30</v>
+      </c>
+      <c r="S12">
+        <v>27000010069</v>
       </c>
       <c r="U12"/>
     </row>
@@ -1391,6 +1424,9 @@
       <c r="N13" t="s">
         <v>71</v>
       </c>
+      <c r="S13">
+        <v>27000010070</v>
+      </c>
       <c r="U13" s="4"/>
     </row>
     <row r="14" spans="1:21">
@@ -1420,6 +1456,9 @@
       <c r="L14" t="s">
         <v>73</v>
       </c>
+      <c r="S14">
+        <v>27000010071</v>
+      </c>
       <c r="U14"/>
     </row>
     <row r="15" spans="1:21">
@@ -1449,6 +1488,9 @@
       <c r="L15" t="s">
         <v>75</v>
       </c>
+      <c r="S15">
+        <v>27000010072</v>
+      </c>
       <c r="U15"/>
     </row>
     <row r="16" spans="1:21">
@@ -1493,6 +1535,9 @@
       <c r="R16" t="s">
         <v>30</v>
       </c>
+      <c r="S16">
+        <v>27000010073</v>
+      </c>
       <c r="U16" s="4" t="s">
         <v>79</v>
       </c>
@@ -1533,6 +1578,9 @@
       <c r="N17" t="s">
         <v>28</v>
       </c>
+      <c r="S17">
+        <v>27000010074</v>
+      </c>
       <c r="U17" t="s">
         <v>83</v>
       </c>
@@ -1577,6 +1625,9 @@
       </c>
       <c r="R18" t="s">
         <v>30</v>
+      </c>
+      <c r="S18">
+        <v>27000010075</v>
       </c>
       <c r="U18"/>
     </row>
@@ -1619,6 +1670,9 @@
       <c r="R19" t="s">
         <v>30</v>
       </c>
+      <c r="S19">
+        <v>27000010076</v>
+      </c>
       <c r="U19"/>
     </row>
     <row r="20" spans="1:21">
@@ -1665,6 +1719,9 @@
       <c r="R20" t="s">
         <v>30</v>
       </c>
+      <c r="S20">
+        <v>27000010077</v>
+      </c>
       <c r="U20"/>
     </row>
     <row r="21" spans="1:21">
@@ -1708,6 +1765,9 @@
       <c r="R21" t="s">
         <v>30</v>
       </c>
+      <c r="S21">
+        <v>27000010078</v>
+      </c>
       <c r="U21"/>
     </row>
     <row r="22" spans="1:21">
@@ -1751,6 +1811,9 @@
       <c r="R22" t="s">
         <v>30</v>
       </c>
+      <c r="S22">
+        <v>27000010079</v>
+      </c>
       <c r="U22"/>
     </row>
     <row r="23" spans="1:21">
@@ -1793,6 +1856,9 @@
       </c>
       <c r="R23" t="s">
         <v>30</v>
+      </c>
+      <c r="S23">
+        <v>27000010080</v>
       </c>
       <c r="U23"/>
     </row>
@@ -1835,6 +1901,9 @@
       <c r="R24" t="s">
         <v>104</v>
       </c>
+      <c r="S24">
+        <v>27000010081</v>
+      </c>
       <c r="U24"/>
     </row>
     <row r="25" spans="1:21">
@@ -1878,6 +1947,9 @@
       <c r="R25" t="s">
         <v>107</v>
       </c>
+      <c r="S25">
+        <v>27000010082</v>
+      </c>
       <c r="U25"/>
     </row>
     <row r="26" spans="1:21">
@@ -1924,6 +1996,9 @@
       <c r="R26" t="s">
         <v>30</v>
       </c>
+      <c r="S26">
+        <v>27000010083</v>
+      </c>
       <c r="U26"/>
     </row>
     <row r="27" spans="1:21">
@@ -1963,6 +2038,9 @@
       </c>
       <c r="N27" t="s">
         <v>115</v>
+      </c>
+      <c r="S27">
+        <v>27000010084</v>
       </c>
       <c r="U27" s="4"/>
     </row>
@@ -2005,6 +2083,9 @@
       <c r="R28" t="s">
         <v>111</v>
       </c>
+      <c r="S28">
+        <v>27000010085</v>
+      </c>
       <c r="U28" s="4"/>
     </row>
     <row r="29" spans="1:21">
@@ -2041,6 +2122,9 @@
       </c>
       <c r="N29" t="s">
         <v>28</v>
+      </c>
+      <c r="S29">
+        <v>27000010086</v>
       </c>
       <c r="U29"/>
     </row>
@@ -2085,6 +2169,9 @@
       </c>
       <c r="R30" t="s">
         <v>111</v>
+      </c>
+      <c r="S30">
+        <v>27000010087</v>
       </c>
       <c r="U30" t="s">
         <v>121</v>
